--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855681</v>
       </c>
       <c r="B2" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,9 +799,741 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136481268</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93393</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>406977</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6850709</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136481268</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136481269</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93393</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>406973</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6850623</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136481269</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136481018</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93399</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>407203</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6850779</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136481018</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136481019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93399</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>407132</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6850772</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136481019</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136481020</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93399</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>407177</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6850744</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136481020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136481259</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93399</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>406987</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6850613</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136481259</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855681</v>
       </c>
       <c r="B2" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481268</v>
       </c>
       <c r="B3" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136481269</v>
       </c>
       <c r="B4" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136481018</v>
       </c>
       <c r="B5" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136481019</v>
       </c>
       <c r="B6" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136481020</v>
       </c>
       <c r="B7" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136481259</v>
       </c>
       <c r="B8" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36873-2026 artfynd.xlsx
+++ b/artfynd/A 36873-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136481018</v>
+        <v>136583117</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,26 +1054,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407203</v>
+        <v>406975</v>
       </c>
       <c r="R5" t="n">
-        <v>6850779</v>
+        <v>6850621</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,22 +1112,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:36</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:36</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1158,13 +1148,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136481018</t>
+          <t>https://artportalen.se/Sighting/136583117</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136481019</v>
+        <v>136481018</v>
       </c>
       <c r="B6" t="n">
         <v>93400</v>
@@ -1194,7 +1184,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1203,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407132</v>
+        <v>407203</v>
       </c>
       <c r="R6" t="n">
-        <v>6850772</v>
+        <v>6850779</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1238,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1279,13 +1269,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136481019</t>
+          <t>https://artportalen.se/Sighting/136481018</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136481020</v>
+        <v>136481019</v>
       </c>
       <c r="B7" t="n">
         <v>93400</v>
@@ -1315,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407177</v>
+        <v>407132</v>
       </c>
       <c r="R7" t="n">
-        <v>6850744</v>
+        <v>6850772</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1359,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1400,13 +1390,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136481020</t>
+          <t>https://artportalen.se/Sighting/136481019</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136481259</v>
+        <v>136481020</v>
       </c>
       <c r="B8" t="n">
         <v>93400</v>
@@ -1436,7 +1426,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1445,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406987</v>
+        <v>407177</v>
       </c>
       <c r="R8" t="n">
-        <v>6850613</v>
+        <v>6850744</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,22 +1465,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1521,7 +1511,905 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136481020</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136481259</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93400</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>406987</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6850613</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136481259</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136583122</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93400</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>407137</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6850231</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583122</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136583119</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93412</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>407134</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6850327</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583119</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136583121</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93412</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>407139</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6850207</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583121</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136583124</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>407104</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6850329</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583124</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136583123</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79231</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>407104</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6850329</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583123</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136583120</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79232</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>407200</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6850085</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583120</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136583118</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80064</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>407107</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6850329</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583118</t>
         </is>
       </c>
     </row>
@@ -1534,6 +2422,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
